--- a/artfynd/A 56399-2025 artfynd.xlsx
+++ b/artfynd/A 56399-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131126459</v>
       </c>
       <c r="B3" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56399-2025 artfynd.xlsx
+++ b/artfynd/A 56399-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131126459</v>
       </c>
       <c r="B3" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56399-2025 artfynd.xlsx
+++ b/artfynd/A 56399-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131126459</v>
       </c>
       <c r="B3" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56399-2025 artfynd.xlsx
+++ b/artfynd/A 56399-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131126459</v>
       </c>
       <c r="B3" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56399-2025 artfynd.xlsx
+++ b/artfynd/A 56399-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131126459</v>
       </c>
       <c r="B3" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56399-2025 artfynd.xlsx
+++ b/artfynd/A 56399-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131126459</v>
       </c>
       <c r="B3" t="n">
-        <v>58051</v>
+        <v>58056</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
